--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2428,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2539,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2650,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2761,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2872,1240 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1235,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1490,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1534,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1592,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1601,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1653,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1712,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,33 +1772,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,12 +1941,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1982,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,12 +2290,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2267,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,10 +2331,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2378,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3889,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3936,7 +4004,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4051,7 +4119,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4100,10 +4168,811 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
         </is>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1602,24 +1602,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1830,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1863,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,33 +1891,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2068,32 +2076,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,33 +2137,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2179,32 +2195,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2212,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,33 +2256,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2319,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq44推进至seq63，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,32 +2437,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2446,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2470,33 +2498,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2628,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2635,32 +2667,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2668,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,33 +2728,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2786,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2779,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,33 +2847,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3001,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3112,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4173,7 +4221,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4397,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4508,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4514,7 +4562,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4623,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4629,7 +4677,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4738,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4744,7 +4792,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4853,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4854,12 +4902,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4968,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4969,12 +5017,1035 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3016,32 +3016,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3077,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3093,13 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3127,32 +3135,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3160,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,33 +3196,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3238,32 +3254,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3271,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,17 +3315,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3315,13 +3335,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3349,32 +3373,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3382,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3406,17 +3434,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3426,13 +3454,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3460,32 +3492,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3493,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,33 +3553,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,32 +3722,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,33 +3783,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3841,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3826,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,33 +3902,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3991,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4019,32 +4075,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4052,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4076,17 +4136,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4096,12 +4156,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4134,32 +4194,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4167,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4191,37 +4255,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4249,32 +4313,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4282,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4306,37 +4374,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4432,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq52，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4397,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4405,10 +4473,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4508,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4562,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4590,32 +4674,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4623,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4647,17 +4735,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4667,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4777,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4792,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4892,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4907,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4968,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5022,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5137,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5252,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5367,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5482,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5654,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5708,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5823,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5995,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6039,13 +6127,937 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,13 +2633,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2747,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2758,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3226,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3813,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4441,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq52，推进23站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq63，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,32 +4563,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4592,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4624,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4636,17 +4644,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4684,24 +4692,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4711,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4793,32 +4801,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4826,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4862,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,17 +4882,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4908,32 +4920,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4941,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4981,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4985,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5039,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5056,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5100,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5158,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5171,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5219,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,17 +5239,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5253,32 +5277,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5286,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5338,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5330,17 +5358,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5396,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5401,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,37 +5457,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5587,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5570,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5630,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5631,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5691,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,13 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5796,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5896,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5911,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5972,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6083,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6137,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6252,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6367,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6482,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6597,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6712,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6827,7 +6867,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6932,17 +6972,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7047,17 +7087,584 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>11/28</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,17 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2986,13 +2986,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,17 +3100,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,14 +3457,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3577,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4278,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4289,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4777,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4842,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4892,7 +4896,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5015,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5134,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5515,32 +5519,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5548,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5580,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5592,17 +5600,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5648,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5667,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,12 +5724,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5749,32 +5757,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5782,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5818,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5826,17 +5838,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5876,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5897,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5937,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5941,17 +5957,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5979,32 +5995,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6012,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6056,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6056,13 +6076,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6114,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6123,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,32 +6175,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6205,32 +6233,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6238,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,37 +6294,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6352,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6353,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6413,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6397,17 +6433,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6471,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6468,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,37 +6532,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,7 +6777,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6752,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6867,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6982,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7323,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7539,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7654,17 +7694,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>22/28</t>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6590,32 +6590,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6623,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,17 +6651,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6667,17 +6671,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6705,32 +6709,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6738,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6770,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6782,17 +6790,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6935,32 +6943,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6968,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,17 +7004,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7012,17 +7024,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7309,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7363,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7535,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7589,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7765,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7819,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7995,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,17 +8281,132 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,18 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4001,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,17 +4406,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,14 +4766,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -4777,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4886,12 +4890,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4961,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5000,22 +5004,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5491,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5610,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5967,7 +5971,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6205,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6324,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6746,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6800,7 +6804,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6828,32 +6832,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6861,7 +6869,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6893,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6905,17 +6913,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6961,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6980,7 +6988,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,22 +7027,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7062,32 +7070,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7095,7 +7107,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,17 +7131,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7139,12 +7151,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7177,32 +7189,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7210,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,33 +7250,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7375,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7601,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7716,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8122,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8291,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8410,6 +8430,351 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,14 +2275,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>149.5</t>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,13 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2522,17 +2526,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2760,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,17 +3113,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,17 +3232,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3342,14 +3346,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>159.0</t>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3476,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3710,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3825,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4297,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4536,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4543,7 +4547,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4781,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4895,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5019,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,14 +5246,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -5257,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5361,14 +5365,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>149.5</t>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5485,17 +5489,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5604,17 +5608,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5737,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5856,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5961,17 +5965,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6199,17 +6203,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6322,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6451,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6566,7 +6570,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6804,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7042,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7080,24 +7084,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7107,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7156,12 +7160,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7203,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -7226,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7275,12 +7279,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7308,32 +7312,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7341,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7373,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7385,17 +7393,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7423,32 +7431,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7456,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7492,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7500,13 +7512,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7534,32 +7550,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7567,7 +7587,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,17 +7611,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7611,17 +7631,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7649,32 +7669,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7682,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7730,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7726,17 +7750,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7764,32 +7788,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7797,7 +7825,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7849,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7841,17 +7869,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7907,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7912,7 +7944,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7968,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7956,17 +7988,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8081,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8196,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8343,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8541,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8656,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8766,12 +8798,579 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3819,17 +3819,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,14 +4167,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6560,17 +6560,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6798,17 +6798,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7917,24 +7917,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8026,32 +8026,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8059,7 +8063,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,17 +8087,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8103,17 +8107,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8141,32 +8145,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8174,7 +8182,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,17 +8206,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8218,17 +8226,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8256,32 +8264,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8289,7 +8301,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8325,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8333,17 +8345,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8519,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8646,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8688,7 +8700,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8864,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8975,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9029,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9263,22 +9275,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9311,12 +9323,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9355,22 +9367,1053 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>149.5</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,14 +1549,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,14 +2755,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,22 +3465,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4048,22 +4048,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,14 +5960,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7150,14 +7150,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7274,17 +7274,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,14 +7626,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8155,19 +8155,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8221,22 +8221,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8383,32 +8383,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8416,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,37 +8444,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8498,32 +8502,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8531,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8563,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8575,12 +8583,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8613,32 +8621,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8646,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8670,37 +8682,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8728,32 +8740,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8761,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8785,17 +8801,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8805,17 +8821,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8843,12 +8859,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq42，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8876,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,10 +8900,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 33分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8954,32 +8986,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8987,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9047,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9031,17 +9067,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9439,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9723,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10014,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10129,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10244,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10298,7 +10334,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10417,6 +10453,696 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3346,22 +3346,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3699,18 +3699,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3833,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3948,7 +3952,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4063,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4370,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4420,7 +4424,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4547,7 +4551,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4666,7 +4670,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4735,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4785,7 +4789,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4854,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5142,7 +5146,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5211,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5246,22 +5250,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5365,22 +5369,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5449,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5622,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5741,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5846,17 +5850,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5925,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5975,7 +5979,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,7 +6083,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6094,7 +6098,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6217,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6317,14 +6321,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -6332,7 +6336,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6440,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6451,7 +6455,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6574,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6639,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6689,7 +6693,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6812,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6877,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6927,7 +6931,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7165,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7273,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7284,7 +7288,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7403,7 +7407,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7512,17 +7516,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7641,7 +7645,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7864,14 +7868,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>136.7</t>
@@ -7879,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8002,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8121,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8236,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8359,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8474,7 +8478,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8597,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8712,7 +8716,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8816,7 +8820,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8831,7 +8835,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8868,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq42，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8892,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8958,7 +8962,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8996,24 +9000,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9023,7 +9027,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,22 +9066,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9192,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9216,32 +9220,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9249,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,37 +9281,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9331,32 +9339,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9364,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,33 +9400,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9442,32 +9458,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9475,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9499,37 +9519,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9557,32 +9577,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9590,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9614,17 +9638,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9634,17 +9658,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9672,32 +9696,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9705,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,17 +9757,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9749,17 +9777,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9874,7 +9902,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9974,7 +10002,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9989,7 +10017,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10104,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10219,7 +10247,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10334,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10449,7 +10477,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10564,7 +10592,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10679,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10794,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10909,7 +10937,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11024,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11139,7 +11167,1038 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>148.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2874,22 +2874,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3937,22 +3937,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4655,22 +4655,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6678,22 +6678,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9587,24 +9587,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9706,24 +9706,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9772,22 +9772,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9815,32 +9815,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9848,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9872,37 +9876,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9930,32 +9934,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9963,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,17 +9995,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -10007,17 +10015,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10045,32 +10053,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10078,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10102,37 +10114,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10160,32 +10172,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10193,7 +10209,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,37 +10233,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10378,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10390,32 +10406,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10423,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10447,17 +10467,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10467,12 +10487,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10538,7 +10558,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10592,7 +10612,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10727,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10788,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10822,7 +10842,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10937,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11052,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11167,7 +11187,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11282,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11458,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11512,7 +11532,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11684,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11738,7 +11758,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11853,7 +11873,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,17 +11978,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12198,7 +12218,582 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>148.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10492,12 +10492,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12686,22 +12686,22 @@
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -12734,12 +12734,12 @@
       <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12753,45 +12753,160 @@
       <c r="T104" s="2" t="inlineStr"/>
       <c r="U104" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr">
+      <c r="W105" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X104" s="2" t="inlineStr">
+      <c r="X105" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y104" s="2" t="inlineStr">
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z104" s="2" t="inlineStr">
+      <c r="Z105" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA104" s="2" t="inlineStr">
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
         <is>
           <t>148.7</t>
         </is>
       </c>
-      <c r="AC104" s="2" t="inlineStr">
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
         </is>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,17 +2989,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5131,22 +5131,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5493,17 +5493,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5969,17 +5969,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6326,17 +6326,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7397,17 +7397,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7635,17 +7635,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8468,17 +8468,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10291,32 +10291,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10324,7 +10328,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10348,37 +10352,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10501,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10525,32 +10529,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10558,7 +10566,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10582,17 +10590,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10602,17 +10610,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10640,32 +10648,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10673,7 +10685,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10697,17 +10709,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10717,17 +10729,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10755,32 +10767,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10788,7 +10804,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10812,17 +10828,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10832,17 +10848,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10870,32 +10886,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10903,7 +10923,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10927,17 +10947,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10947,17 +10967,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10985,32 +11005,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11018,7 +11042,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11042,17 +11066,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11062,17 +11086,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11100,32 +11124,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11133,7 +11161,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11157,17 +11185,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11177,17 +11205,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11276,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11302,7 +11330,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11330,32 +11358,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11363,7 +11395,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,32 +11419,32 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11445,32 +11477,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11478,7 +11514,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11502,17 +11538,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11522,17 +11558,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11629,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11704,7 +11740,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11758,7 +11794,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11855,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11873,7 +11909,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11970,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11988,7 +12024,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12164,7 +12200,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12218,7 +12254,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12315,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12333,7 +12369,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12430,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12448,7 +12484,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12545,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12624,7 +12660,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12678,7 +12714,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12775,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12793,7 +12829,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12890,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12908,7 +12944,237 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>147.7</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3704,17 +3704,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5255,17 +5255,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5850,17 +5850,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9301,17 +9301,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9420,17 +9420,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9539,17 +9539,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11487,12 +11487,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11707,32 +11707,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11740,7 +11744,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11764,17 +11768,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11784,17 +11788,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11822,32 +11826,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11855,7 +11863,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11879,17 +11887,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11899,17 +11907,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11937,12 +11945,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11970,7 +11978,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11978,10 +11986,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="S97" s="2" t="inlineStr"/>
-      <c r="T97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12024,7 +12044,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12052,32 +12072,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12085,7 +12109,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12109,17 +12133,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12129,17 +12153,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12167,32 +12191,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12200,7 +12228,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12224,17 +12252,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12244,17 +12272,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12282,12 +12310,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq47，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12315,7 +12343,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12323,10 +12351,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12430,7 +12474,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12484,7 +12528,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12589,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12627,32 +12671,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12660,7 +12708,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12684,17 +12732,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12704,17 +12752,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12823,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12829,7 +12877,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12938,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12944,7 +12992,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -13005,7 +13053,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13059,7 +13107,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13168,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">

--- a/data/export/2026-10-15-浦东35路.xlsx
+++ b/data/export/2026-10-15-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4660,17 +4660,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7992,17 +7992,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9896,17 +9896,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11215,7 +11215,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12201,24 +12201,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12556,32 +12556,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12589,7 +12593,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12613,17 +12617,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12633,17 +12637,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12681,19 +12685,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12708,7 +12712,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12757,12 +12761,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12790,32 +12794,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12823,7 +12831,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12847,17 +12855,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12867,17 +12875,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12905,32 +12913,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12938,7 +12950,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12962,17 +12974,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12982,17 +12994,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13065,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13107,7 +13119,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13180,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
